--- a/data/trans_dic/P74B-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P74B-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su pareja percibe algún tipo de pensión</t>
+          <t>Población que su pareja percibe algún tipo de pensión (tasa de respuesta: 96,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,54</t>
+          <t>6,23; 12,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,11; 21,05</t>
+          <t>11,71; 20,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,35; 15,57</t>
+          <t>7,97; 15,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78,46; 90,11</t>
+          <t>78,93; 90,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,76; 67,59</t>
+          <t>53,11; 67,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,46; 73,48</t>
+          <t>60,09; 72,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,24; 36,66</t>
+          <t>28,64; 37,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,08; 38,26</t>
+          <t>28,79; 38,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,19; 38,81</t>
+          <t>29,98; 38,9</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 11,16</t>
+          <t>5,87; 11,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,98; 16,23</t>
+          <t>9,34; 16,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,15; 17,55</t>
+          <t>10,04; 17,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,93; 90,97</t>
+          <t>79,25; 90,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,31; 71,24</t>
+          <t>59,45; 71,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,17; 70,27</t>
+          <t>58,07; 69,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,83; 33,45</t>
+          <t>25,86; 33,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,37; 37,94</t>
+          <t>30,28; 37,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,86; 38,35</t>
+          <t>30,34; 38,06</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,72</t>
+          <t>2,91; 8,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 14,9</t>
+          <t>7,42; 15,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,19; 11,67</t>
+          <t>5,28; 11,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71,14; 85,66</t>
+          <t>71,75; 85,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60,95; 75,3</t>
+          <t>61,11; 74,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>55,97; 69,37</t>
+          <t>56,18; 69,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,74; 29,84</t>
+          <t>21,78; 29,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,65; 38,28</t>
+          <t>29,27; 37,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,0; 33,14</t>
+          <t>24,96; 33,18</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,45; 11,41</t>
+          <t>5,44; 11,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,96; 15,15</t>
+          <t>8,12; 15,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,84; 20,18</t>
+          <t>12,95; 20,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,25; 86,58</t>
+          <t>74,7; 86,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,16; 81,99</t>
+          <t>70,58; 81,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,92; 76,72</t>
+          <t>64,16; 76,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,06; 37,08</t>
+          <t>28,85; 36,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,1; 42,23</t>
+          <t>33,93; 42,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,53; 40,64</t>
+          <t>32,62; 40,66</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,2; 9,08</t>
+          <t>6,17; 9,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,81; 14,6</t>
+          <t>10,81; 14,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,71; 14,32</t>
+          <t>10,83; 14,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79,79; 85,74</t>
+          <t>79,66; 85,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>64,75; 70,87</t>
+          <t>64,87; 71,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,64; 69,35</t>
+          <t>62,96; 69,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,34; 32,26</t>
+          <t>28,29; 32,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,72; 36,83</t>
+          <t>32,85; 36,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,87; 36,1</t>
+          <t>31,98; 35,98</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su pareja percibe algún tipo de pensión</t>
+          <t>Población que su pareja percibe algún tipo de pensión (tasa de respuesta: 96,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20322; 40768</t>
+          <t>20246; 40541</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36402; 63289</t>
+          <t>35222; 62037</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23793; 44379</t>
+          <t>22725; 43959</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113854; 130767</t>
+          <t>114532; 131087</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>102107; 130825</t>
+          <t>102792; 129761</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>122649; 149077</t>
+          <t>121911; 147905</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>132791; 172382</t>
+          <t>134684; 174844</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>143705; 189098</t>
+          <t>142285; 187982</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>147299; 189382</t>
+          <t>146296; 189813</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24685; 48360</t>
+          <t>25409; 48290</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37324; 67456</t>
+          <t>38803; 68013</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40131; 69350</t>
+          <t>39701; 68411</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>132636; 150953</t>
+          <t>131506; 150412</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>165116; 198348</t>
+          <t>165514; 199179</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>163000; 196887</t>
+          <t>162709; 195143</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>154759; 200410</t>
+          <t>154964; 199332</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>210761; 263305</t>
+          <t>210108; 261281</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>208474; 259043</t>
+          <t>204925; 257074</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9059; 24412</t>
+          <t>9188; 25823</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19627; 44004</t>
+          <t>21904; 45400</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16527; 37158</t>
+          <t>16817; 36909</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86589; 104262</t>
+          <t>87329; 104462</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>118197; 146040</t>
+          <t>118516; 144955</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>110463; 136900</t>
+          <t>110876; 137436</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95153; 130617</t>
+          <t>95359; 130561</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>140174; 187278</t>
+          <t>143228; 185696</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>128905; 170885</t>
+          <t>128705; 171116</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18598; 38918</t>
+          <t>18572; 37826</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28950; 55108</t>
+          <t>29520; 55751</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46121; 72485</t>
+          <t>46510; 73795</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>133128; 155241</t>
+          <t>133937; 154323</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>179893; 207274</t>
+          <t>178418; 205829</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>138054; 165703</t>
+          <t>138576; 165933</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>151249; 192973</t>
+          <t>150148; 191879</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>210279; 260355</t>
+          <t>209223; 261439</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>187097; 233742</t>
+          <t>187612; 233880</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>87757; 128470</t>
+          <t>87341; 128270</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>148641; 200744</t>
+          <t>148660; 199512</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>145447; 194464</t>
+          <t>147024; 194003</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>488369; 524803</t>
+          <t>487602; 524709</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>594825; 651059</t>
+          <t>595942; 654384</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>561515; 621681</t>
+          <t>564336; 621389</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>574679; 654034</t>
+          <t>573623; 658317</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>750687; 845000</t>
+          <t>753662; 847521</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>718371; 813686</t>
+          <t>720959; 811145</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P74B-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P74B-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,23; 12,47</t>
+          <t>6,16; 12,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,71; 20,63</t>
+          <t>11,72; 20,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,97; 15,42</t>
+          <t>8,21; 15,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78,93; 90,33</t>
+          <t>78,33; 89,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,11; 67,04</t>
+          <t>52,6; 67,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,09; 72,91</t>
+          <t>59,77; 73,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,64; 37,18</t>
+          <t>28,24; 37,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,79; 38,03</t>
+          <t>29,22; 37,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,98; 38,9</t>
+          <t>30,04; 38,57</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 11,15</t>
+          <t>5,79; 11,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 16,37</t>
+          <t>9,46; 16,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,04; 17,31</t>
+          <t>10,22; 17,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79,25; 90,64</t>
+          <t>79,35; 90,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>59,45; 71,54</t>
+          <t>59,03; 71,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,07; 69,65</t>
+          <t>58,53; 70,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,86; 33,27</t>
+          <t>25,63; 33,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,28; 37,65</t>
+          <t>30,21; 37,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,34; 38,06</t>
+          <t>30,82; 38,13</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,17</t>
+          <t>2,97; 7,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,42; 15,37</t>
+          <t>7,18; 15,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 11,59</t>
+          <t>5,38; 11,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71,75; 85,83</t>
+          <t>72,07; 85,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>61,11; 74,74</t>
+          <t>61,17; 75,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56,18; 69,64</t>
+          <t>55,73; 70,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>21,78; 29,82</t>
+          <t>21,85; 30,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29,27; 37,95</t>
+          <t>28,97; 38,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,96; 33,18</t>
+          <t>24,76; 33,1</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,44; 11,09</t>
+          <t>5,6; 11,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,12; 15,33</t>
+          <t>8,0; 15,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,95; 20,55</t>
+          <t>12,67; 20,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,7; 86,07</t>
+          <t>73,87; 86,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,58; 81,42</t>
+          <t>70,8; 81,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,16; 76,82</t>
+          <t>64,2; 76,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,85; 36,87</t>
+          <t>29,04; 37,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>33,93; 42,4</t>
+          <t>34,33; 42,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,62; 40,66</t>
+          <t>32,75; 41,03</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 9,06</t>
+          <t>6,25; 9,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,81; 14,51</t>
+          <t>10,75; 14,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,83; 14,29</t>
+          <t>10,76; 14,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79,66; 85,73</t>
+          <t>79,55; 85,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>64,87; 71,23</t>
+          <t>64,96; 71,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,96; 69,32</t>
+          <t>62,85; 69,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,29; 32,47</t>
+          <t>28,27; 32,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>32,85; 36,94</t>
+          <t>32,8; 36,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,98; 35,98</t>
+          <t>31,73; 35,65</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20246; 40541</t>
+          <t>20022; 40692</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35222; 62037</t>
+          <t>35245; 61545</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22725; 43959</t>
+          <t>23391; 43720</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>114532; 131087</t>
+          <t>113670; 130534</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>102792; 129761</t>
+          <t>101805; 130897</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>121911; 147905</t>
+          <t>121259; 148985</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>134684; 174844</t>
+          <t>132797; 174779</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>142285; 187982</t>
+          <t>144439; 185837</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>146296; 189813</t>
+          <t>146578; 188200</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25409; 48290</t>
+          <t>25062; 50537</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38803; 68013</t>
+          <t>39295; 68579</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39701; 68411</t>
+          <t>40411; 67916</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>131506; 150412</t>
+          <t>131673; 150741</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>165514; 199179</t>
+          <t>164360; 198963</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>162709; 195143</t>
+          <t>163992; 197972</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>154964; 199332</t>
+          <t>153576; 200204</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>210108; 261281</t>
+          <t>209675; 261302</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>204925; 257074</t>
+          <t>208189; 257561</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9188; 25823</t>
+          <t>9397; 24862</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21904; 45400</t>
+          <t>21218; 45837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16817; 36909</t>
+          <t>17112; 36355</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87329; 104462</t>
+          <t>87715; 104556</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>118516; 144955</t>
+          <t>118631; 146006</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>110876; 137436</t>
+          <t>109991; 138187</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95359; 130561</t>
+          <t>95664; 132056</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>143228; 185696</t>
+          <t>141748; 186302</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>128705; 171116</t>
+          <t>127678; 170695</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18572; 37826</t>
+          <t>19110; 38899</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29520; 55751</t>
+          <t>29101; 55032</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46510; 73795</t>
+          <t>45498; 71884</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>133937; 154323</t>
+          <t>132449; 154623</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>178418; 205829</t>
+          <t>178972; 206148</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>138576; 165933</t>
+          <t>138661; 166199</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>150148; 191879</t>
+          <t>151101; 193820</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>209223; 261439</t>
+          <t>211660; 262077</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>187612; 233880</t>
+          <t>188381; 235972</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>87341; 128270</t>
+          <t>88479; 128871</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>148660; 199512</t>
+          <t>147863; 200353</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>147024; 194003</t>
+          <t>146154; 195350</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>487602; 524709</t>
+          <t>486902; 525540</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>595942; 654384</t>
+          <t>596811; 652904</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>564336; 621389</t>
+          <t>563374; 623986</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>573623; 658317</t>
+          <t>573265; 654471</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>753662; 847521</t>
+          <t>752333; 845417</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>720959; 811145</t>
+          <t>715239; 803734</t>
         </is>
       </c>
     </row>
